--- a/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
@@ -594,16 +594,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -617,16 +620,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>86.84</v>
+      </c>
+      <c r="H3">
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -714,7 +720,7 @@
         <v>95</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -731,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H3">
         <v>9.199999999999999</v>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
@@ -620,19 +620,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -646,16 +646,19 @@
         <v>36</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>36</v>
       </c>
-      <c r="E4">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
@@ -775,7 +775,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20222.xlsx
@@ -723,7 +723,7 @@
         <v>95</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>89.47</v>
+        <v>86.84</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
